--- a/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
+++ b/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excl. Outliers" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outliers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals 3-Way" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +62,10 @@
     <font>
       <i val="1"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,6 +141,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2031,7 +2043,7 @@
         <v>550.49</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
@@ -4661,7 +4673,7 @@
         <v>550.49</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
@@ -7733,4 +7745,1654 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Three-Way: iQuote estimate vs SPOT estimate vs ACTUAL job cost (7 produced jobs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ground-truth check. Actuals joined via iQuote sell price. 2 jobs (236869 $2,876.15, 237252 $142.41) could not be matched to an iQuote quote — excluded pending confirmation. Caveats: small sample; actuals may include overs/rework; hand-labor actuals are $0 on every job (likely absorbed elsewhere in MIS costing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>MIS Job</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>SPOT Est / iQuote #</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>SPOT Est $</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>iQuote Est $</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>ACTUAL $</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>SPOT vs Actual</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>iQuote vs Actual</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>236341</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>RW-260623-091031 / 223207</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>267.4</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>320.21</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Job ran DIE CUT; SPOT quoted CAD route — cutting/die not comparable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr"/>
+      <c r="B6" s="11" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>218.57</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>+64%</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr"/>
+      <c r="B7" s="11" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>526.88</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>-23%</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>-21%</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr"/>
+      <c r="B8" s="11" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>1122.58</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1124.91</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1071.74</v>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>+5%</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>+5%</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>236355</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>RW-260727-080830 / 223209</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>+274%</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="11" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>142.18</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>-55%</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>+33%</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr"/>
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr"/>
+      <c r="B16" s="11" t="inlineStr"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr"/>
+      <c r="B17" s="18" t="inlineStr"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>299.32</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>+54%</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>236550</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>RW-260727-102959 / 223393</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>327.76</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>464.78</v>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>-36%</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>917.23</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>-56%</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr"/>
+      <c r="B21" s="11" t="inlineStr"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>104.62</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>248.9</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr"/>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr"/>
+      <c r="B24" s="18" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1192.05</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>919.67</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1630.91</v>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>-44%</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>236688</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>RW-260727-095102 / 223486</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>-42%</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>-38%</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="11" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr"/>
+      <c r="B28" s="11" t="inlineStr"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>154.48</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>-39%</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>-47%</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr"/>
+      <c r="B29" s="11" t="inlineStr"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr"/>
+      <c r="B30" s="11" t="inlineStr"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="B31" s="18" t="inlineStr"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>127.81</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>199.16</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>-38%</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>236802</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>RW-260727-101129 / 223454</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>1479.09</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1507.88</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1053.17</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>+40%</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>+43%</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr"/>
+      <c r="B34" s="11" t="inlineStr"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>2062.33</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>1187.25</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1673.66</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>+23%</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr"/>
+      <c r="B35" s="11" t="inlineStr"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>423.38</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>402.2</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>839.0700000000001</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>-52%</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr"/>
+      <c r="B36" s="11" t="inlineStr"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr"/>
+      <c r="B37" s="11" t="inlineStr"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1293</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr"/>
+      <c r="B38" s="18" t="inlineStr"/>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>4398.3</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>4298.93</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>3565.9</v>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>+23%</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>+21%</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>236822</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>RW-260727-144121 / 223575</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>161.77</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>143.33</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>+13%</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>+12%</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Two SPOT estimates exist for this iQuote; used most recent</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr"/>
+      <c r="B41" s="11" t="inlineStr"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>206.23</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>127.61</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>636.61</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>-68%</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>-80%</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>200.02</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>146.48</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>+29%</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>+37%</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr"/>
+      <c r="B43" s="11" t="inlineStr"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr"/>
+      <c r="B44" s="11" t="inlineStr"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr"/>
+      <c r="B45" s="18" t="inlineStr"/>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>702.2</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>610.12</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>926.42</v>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>236943</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>RW-260722-082345 / 223591</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>1841.01</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>2272.71</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>-65%</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Sold at CAD-pricing option; SPOT quoted Die route</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr"/>
+      <c r="B48" s="11" t="inlineStr"/>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>2331.33</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>801.39</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>4041.83</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>-42%</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>-80%</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr"/>
+      <c r="B49" s="11" t="inlineStr"/>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>461.58</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>2236.98</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>-79%</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>-71%</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr"/>
+      <c r="B50" s="11" t="inlineStr"/>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr"/>
+      <c r="B51" s="11" t="inlineStr"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>916</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>+51%</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr"/>
+      <c r="B52" s="18" t="inlineStr"/>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>5110.18</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>2473.59</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>8551.52</v>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>-71%</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>SOLD PRICE vs ACTUAL COST — would SPOT prices have been viable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>MIS Job</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>iQuote Sold $</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>SPOT Would-Be $</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>ACTUAL Cost $</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Margin as Sold</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>Margin at SPOT Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="n">
+        <v>236341</v>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>1732.96</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>1752.51</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>2276.74</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>-31%</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="n">
+        <v>236355</v>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>453.63</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>+57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n">
+        <v>236550</v>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>1387.27</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>1753.9</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>1630.91</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>-18%</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n">
+        <v>236688</v>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>248.28</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>255.63</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>+19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n">
+        <v>236802</v>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>6164.32</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>5824.4</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>4858.9</v>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>+21%</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n">
+        <v>236822</v>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>1259.41</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>926.42</v>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>+6%</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>+26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="n">
+        <v>236943</v>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>4352.65</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>6773.57</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>9467.52</v>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>-118%</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>15112.47</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>18073.05</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>19561.11</v>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>FINDINGS (small sample — direction, not gospel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>1. These 7 jobs sold for $15,112 but actually cost $19,561 — collectively sold 29% BELOW cost. 4 of 7 lost money as sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>2. At SPOT's prices ($18,073) the same work is nearly break-even (-8%). The earlier '+15.5% SPOT premium' on won jobs was largely justified pricing, not over-pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>3. PRINT: actual $3,594 vs SPOT $3,100 (-14%) vs iQuote $1,926 (-46%), excl blowout job. The +37% SPOT-vs-iQuote print gap = iQuote under-costing print, NOT SPOT over-costing. SPOT print may even be slightly LOW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>4. MATERIAL: SPOT within ±13% of actual — well calibrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>5. CUTTING: BOTH systems under-cost actual by ~30% (SPOT -29%, iQuote -36% excl blowout). Real data now points cutting calibration UP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>6. Blowout job 236943: sold at CAD-pricing $4,353, actual cost $9,468 (-118% margin). SPOT would have quoted $6,774 — still a loss, but $2,400 less of one.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A69:I69"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
+++ b/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
@@ -7753,7 +7753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7770,14 +7770,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Three-Way: iQuote estimate vs SPOT estimate vs ACTUAL job cost (7 produced jobs)</t>
+          <t>Three-Way: iQuote estimate vs SPOT estimate vs ACTUAL job cost (9 produced jobs)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ground-truth check. Actuals joined via iQuote sell price. 2 jobs (236869 $2,876.15, 237252 $142.41) could not be matched to an iQuote quote — excluded pending confirmation. Caveats: small sample; actuals may include overs/rework; hand-labor actuals are $0 on every job (likely absorbed elsewhere in MIS costing).</t>
+          <t>Ground-truth check. Actuals joined via iQuote sell price. All 9 produced jobs included — 236869 and 237252 matched approximately (sold price drifted from quoted; see notes). Caveats: small sample; actuals may include overs/rework; hand-labor actuals are $0 on every job (likely absorbed elsewhere in MIS costing).</t>
         </is>
       </c>
     </row>
@@ -9100,283 +9100,699 @@
       </c>
       <c r="I52" s="18" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>SOLD PRICE vs ACTUAL COST — would SPOT prices have been viable?</t>
-        </is>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>MIS Job</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>iQuote Sold $</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>SPOT Would-Be $</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>ACTUAL Cost $</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>Margin as Sold</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>Margin at SPOT Price</t>
+      <c r="A54" s="11" t="n">
+        <v>236869</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>RW-260730-155412 / 223597</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>662.8200000000001</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>619.83</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>646.66</v>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sold $2,876.15 vs quoted $2,749.42 — order-time adjustment; 2 SPOT estimates exist, used most recent</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
-        <v>236341</v>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>1732.96</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>1752.51</v>
+      <c r="A55" s="11" t="inlineStr"/>
+      <c r="B55" s="11" t="inlineStr"/>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>2276.74</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>-31%</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>-30%</t>
-        </is>
-      </c>
+        <v>815.97</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>946.88</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>-59%</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n">
-        <v>236355</v>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>241.9</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>453.63</v>
+      <c r="A56" s="11" t="inlineStr"/>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>193.79</v>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>+57%</t>
-        </is>
-      </c>
+        <v>511.19</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>540.02</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>986.46</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>-48%</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>-45%</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
-        <v>236550</v>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>1387.27</v>
-      </c>
-      <c r="C57" s="11" t="n">
-        <v>1753.9</v>
+      <c r="A57" s="11" t="inlineStr"/>
+      <c r="B57" s="11" t="inlineStr"/>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>1630.91</v>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>-18%</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>+7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n">
-        <v>236688</v>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>248.28</v>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>255.63</v>
+      <c r="A58" s="11" t="inlineStr"/>
+      <c r="B58" s="11" t="inlineStr"/>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>206.83</v>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>+19%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
-        <v>236802</v>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>6164.32</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>5824.4</v>
-      </c>
-      <c r="D59" s="11" t="n">
-        <v>4858.9</v>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>+21%</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="n">
-        <v>236822</v>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>985.09</v>
-      </c>
-      <c r="C60" s="11" t="n">
-        <v>1259.41</v>
-      </c>
-      <c r="D60" s="11" t="n">
-        <v>926.42</v>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>+6%</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>+26%</t>
-        </is>
-      </c>
+      <c r="A59" s="18" t="inlineStr"/>
+      <c r="B59" s="18" t="inlineStr"/>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>2134.98</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>1666.48</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>-17%</t>
+        </is>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>-35%</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
+        <v>237252</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>RW-260724-113737 / 223651</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sold $142.41 sits between qty-22 ($130.54) and qty-59 ($157.17) scenarios — matched qty 22; actual material not recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr"/>
+      <c r="B62" s="11" t="inlineStr"/>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr"/>
+      <c r="B63" s="11" t="inlineStr"/>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>-63%</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>-75%</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr"/>
+      <c r="B64" s="11" t="inlineStr"/>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr"/>
+      <c r="B65" s="11" t="inlineStr"/>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Die</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr"/>
+      <c r="B66" s="18" t="inlineStr"/>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (excl die)</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>-60%</t>
+        </is>
+      </c>
+      <c r="H66" s="21" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>SOLD PRICE vs ACTUAL COST — would SPOT prices have been viable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>MIS Job</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>iQuote Sold $</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>SPOT Would-Be $</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>ACTUAL Cost $</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Margin as Sold</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Margin at SPOT Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="n">
+        <v>236341</v>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>1732.96</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>1752.51</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>2276.74</v>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>-31%</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="n">
+        <v>236355</v>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>453.63</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>+57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="n">
+        <v>236550</v>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>1387.27</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>1753.9</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>1630.91</v>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>-18%</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="n">
+        <v>236688</v>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>248.28</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>255.63</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>+19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="n">
+        <v>236802</v>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>6164.32</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>5824.4</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>4858.9</v>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>+21%</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="n">
+        <v>236822</v>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>1259.41</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>926.42</v>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>+6%</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>+26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="n">
         <v>236943</v>
       </c>
-      <c r="B61" s="11" t="n">
+      <c r="B75" s="11" t="n">
         <v>4352.65</v>
       </c>
-      <c r="C61" s="11" t="n">
+      <c r="C75" s="11" t="n">
         <v>6773.57</v>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D75" s="11" t="n">
         <v>9467.52</v>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>-118%</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>-40%</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="11" t="n">
+        <v>236869</v>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>2876.15</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>3071.43</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>2580</v>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>+16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="n">
+        <v>237252</v>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>142.41</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n">
-        <v>15112.47</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>18073.05</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>19561.11</v>
-      </c>
-      <c r="E62" s="22" t="inlineStr">
-        <is>
-          <t>-29%</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="B78" s="4" t="n">
+        <v>18131.03</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>21276.87</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>22305.08</v>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>-23%</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>FINDINGS (small sample — direction, not gospel)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>1. These 7 jobs sold for $15,112 but actually cost $19,561 — collectively sold 29% BELOW cost. 4 of 7 lost money as sold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>2. At SPOT's prices ($18,073) the same work is nearly break-even (-8%). The earlier '+15.5% SPOT premium' on won jobs was largely justified pricing, not over-pricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>3. PRINT: actual $3,594 vs SPOT $3,100 (-14%) vs iQuote $1,926 (-46%), excl blowout job. The +37% SPOT-vs-iQuote print gap = iQuote under-costing print, NOT SPOT over-costing. SPOT print may even be slightly LOW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="26" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>4. MATERIAL: SPOT within ±13% of actual — well calibrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>5. CUTTING: BOTH systems under-cost actual by ~30% (SPOT -29%, iQuote -36% excl blowout). Real data now points cutting calibration UP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>1. These 9 jobs sold for $18,131 but actually cost $22,305 — collectively sold 23% BELOW cost. 5 of 9 lost money as sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>2. At SPOT's prices ($21,277) the same work is nearly break-even (-5%). The earlier '+15.5% SPOT premium' on won jobs was largely justified pricing, not over-pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>3. PRINT: actual $4,541 vs SPOT -14% vs iQuote -49%, excl blowout job. The +37% SPOT-vs-iQuote print gap = iQuote under-costing print, NOT SPOT over-costing. SPOT print may even be slightly LOW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>4. MATERIAL: SPOT within ±10% of actual — well calibrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>5. CUTTING: BOTH systems under-cost actual (SPOT -37%, iQuote -41% excl blowout). Real data now points cutting calibration UP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>6. Blowout job 236943: sold at CAD-pricing $4,353, actual cost $9,468 (-118% margin). SPOT would have quoted $6,774 — still a loss, but $2,400 less of one.</t>
         </is>
@@ -9384,14 +9800,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A86:I86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
+++ b/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
@@ -9787,14 +9787,14 @@
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>5. CUTTING: BOTH systems under-cost actual (SPOT -37%, iQuote -41% excl blowout). Real data now points cutting calibration UP.</t>
+          <t>5. CUTTING (machine-family aligned, excl 236943 route mismatch): CAD route SPOT -32% vs actual (7 jobs); Crest -50% (1 job). Per-job spread (+33% to -63%) suggests difficulty/setup scaling misses, not a flat rate error. Real data points cutting calibration UP.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>6. Blowout job 236943: sold at CAD-pricing $4,353, actual cost $9,468 (-118% margin). SPOT would have quoted $6,774 — still a loss, but $2,400 less of one.</t>
+          <t>6. Blowout job 236943: sold at CAD-pricing $4,353, actual cost $9,468 (-118% margin). SPOT would have quoted $6,774 — still a loss, but $2,400 less of one. NOTE: SPOT quoted Crest/die route but job ran Kongsberg (CAD) — excluded from cutting calibration. 237252 confirmed cut-only op (no material).</t>
         </is>
       </c>
     </row>

--- a/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
+++ b/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outliers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals 3-Way" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutting Deep-Dive" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -113,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,6 +149,10 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9811,4 +9816,725 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cutting Cost Deep-Dive — 1 year of wide-format production (1,045 cutting ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. MACHINE MIX &amp; RATES (why "blended vs LG Zund" is moot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Work center</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Ops %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Cost $</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Cost %</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>WC rate $/hr</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>$/op</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Kongsburg</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>351</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>152001</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2111.1</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Clamshell Diecutter</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>148242</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>776.1</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>191.00</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>LG Zund</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>405</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>127455</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1847.2</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Sm Zund</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>133</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>41079</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>595.3</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Bobst Die Cutter</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>4169</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>CAD-family rates are uniform ($69-72/hr) — machine drift at schedule time is NOT a rate risk. Blended CAD rate remains the right model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2. HOURS DECOMPOSITION — 9 produced jobs (SPOT estimated vs actual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>MIS Job</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Machine ran</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>SPOT hrs</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Actual hrs</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Hours Δ</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>SPOT $/hr</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Actual WC $/hr</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>SPOT cut $</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>Actual cut $</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>236341</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Kongsburg</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>-60%</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>408</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>236355</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>LG Zund</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>236550</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Kongsburg</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>-53%</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>225</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>236688</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Sm Zund</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>-70%</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>94</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>236802</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Clamshell Diecutter</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>191.00</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>423</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>236822</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>LG Zund</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>-35%</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>236943</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Kongsburg</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>462</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>236869</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Kongsburg</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>511</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>237252</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>LG Zund</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>-82%</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>3. ROOT CAUSE &amp; BOOKMARKED RECOMMENDATION (NO CHANGES APPLIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>• Setup: SPOT assumes 25 min (Standard). Logged actual setups: LG Zund ~16 min, Sm Zund ~18, Kongsberg ~32 median. SETUP IS FINE. (Caveat: setup logging inconsistent — ~40% of ops log none; those hours sit inside run time.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>• Run speed: SPOT assumes 650 in/min cut speed. Effective actual throughput (total-hours method, robust to the setup logging issue): ~165 in/min — ~3.5x slower. THIS IS THE MISS. 650 is plausibly head speed; real throughput includes sheet load/unload/registration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>• Rate: SPOT charges $138/hr vs actual CAD-family WC rate $69-72/hr. The inflated rate historically masked ~half of the speed miss (compensating errors).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>RECOMMENDED FIX (admin console only, reversible, BOOKMARKED pending leadership):</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Option B (preferred): cadRegularSpeed 650 → ~165 in/min  AND  cadRate $138 → $72/hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Costs land the same place as Option A but hours become real — which also fixes route auto-selection fairness (CAD vs Crest vs Bobst compete on honest numbers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Option A (single knob): cadRate $138 → ~$203/hr. Quicker, but hours stay fictional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Either way: revisit at ~25 produced Test-flagged jobs. Speed fit is based on 5 jobs with known rule inches — thin but consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Crest: rate already matches WC ($191). Crest hours also ~50% low on the one produced crest job — insufficient data to act (n=1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ask of production: consistent setup logging on Zunds/Kongsberg would let the next pull separate setup vs run cleanly and validate the difficulty curve.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A30:I30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
+++ b/frontend/public/SPOT_vs_iQuote_Analysis.xlsx
@@ -7786,6 +7786,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -8017,6 +8018,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="11" t="n">
         <v>236355</v>
@@ -8197,6 +8199,7 @@
       </c>
       <c r="I17" s="18" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="11" t="n">
         <v>236550</v>
@@ -8377,6 +8380,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="11" t="n">
         <v>236688</v>
@@ -8557,6 +8561,7 @@
       </c>
       <c r="I31" s="18" t="inlineStr"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="n">
         <v>236802</v>
@@ -8737,6 +8742,7 @@
       </c>
       <c r="I38" s="18" t="inlineStr"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="11" t="n">
         <v>236822</v>
@@ -8921,6 +8927,7 @@
       </c>
       <c r="I45" s="18" t="inlineStr"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="11" t="n">
         <v>236943</v>
@@ -9105,6 +9112,7 @@
       </c>
       <c r="I52" s="18" t="inlineStr"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="11" t="n">
         <v>236869</v>
@@ -9289,6 +9297,7 @@
       </c>
       <c r="I59" s="18" t="inlineStr"/>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="11" t="n">
         <v>237252</v>
@@ -9476,7 +9485,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>SOLD PRICE vs ACTUAL COST — would SPOT prices have been viable?</t>
+          <t>INVOICED PRICE vs ACTUAL COST — would SPOT prices have been viable?</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9497,7 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>iQuote Sold $</t>
+          <t>Invoiced $</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
@@ -9503,7 +9512,7 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Margin as Sold</t>
+          <t>Margin as Invoiced</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -9754,6 +9763,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
@@ -9764,7 +9774,7 @@
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>1. These 9 jobs sold for $18,131 but actually cost $22,305 — collectively sold 23% BELOW cost. 5 of 9 lost money as sold.</t>
+          <t>1. These 9 jobs invoiced $18,131 but actually cost $22,305 — collectively invoiced 23% BELOW cost. 5 of 9 lost money as invoiced.</t>
         </is>
       </c>
     </row>
